--- a/y11486/cleaned_rework.xlsx
+++ b/y11486/cleaned_rework.xlsx
@@ -190,13 +190,13 @@
     <t>2024-01-20 00:00:00</t>
   </si>
   <si>
-    <t>2026-05-25 03:29:47</t>
-  </si>
-  <si>
-    <t>2026-05-25 03:30:58</t>
-  </si>
-  <si>
-    <t>2026-05-25 03:32:35</t>
+    <t>2026-05-25 04:16:51</t>
+  </si>
+  <si>
+    <t>2026-05-25 04:17:01</t>
+  </si>
+  <si>
+    <t>2026-05-25 04:17:25</t>
   </si>
 </sst>
 </file>
